--- a/nudges.xlsx
+++ b/nudges.xlsx
@@ -441,27 +441,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>family_structure</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>access_level</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>frequency_level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>access_level</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>age</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>grade_level</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -493,35 +493,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>List 3 things in the room that are your favorite color. Say them out loud!</t>
+          <t>Close your eyes and listen carefully. What are 3 sounds you can hear?</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -533,35 +533,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stand up and stretch like a cat for 10 seconds. Reach high, then low!</t>
+          <t>Jump in place 10 times to get your energy out!</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Close your eyes and name 5 things you can hear around you right now.</t>
+          <t>List 5 things that make you unique and special!</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -586,19 +586,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -607,20 +607,20 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Whisper the alphabet backwards while walking heel-to-toe like a tightrope walker.</t>
+          <t>Balance on one foot for 20 seconds. Switch feet and try again!</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -629,13 +629,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -644,38 +644,38 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Close your eyes and imagine your favorite place. What do you see, hear, and smell there?</t>
+          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -693,38 +693,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Squeeze a stress ball 10 times with each hand. Imagine squeezing out all the worries.</t>
+          <t>Walk slowly around the room, paying attention to how your feet feel with each step.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -733,7 +733,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Make a silly face in the mirror and hold it for 5 seconds. Can you make yourself laugh?</t>
+          <t>Imagine you're holding a bubble wand. Slowly blow 3 imaginary bubbles and watch them float away.</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -743,108 +743,108 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Make a silly face in the mirror and hold it for 5 seconds. Repeat until you smile!</t>
+          <t>Think of someone you care about. Send them good thoughts in your mind.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Walk like a penguin from one side of the room to the other. Waddle slowly!</t>
+          <t>Fold a piece of paper into the smallest square you can make. Then unfold it and try again!</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -853,26 +853,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Write down one worry, then crumple the paper and throw it away like a basketball.</t>
+          <t>Trace your hand on paper and write one strength you have in each finger.</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hum your favorite song quietly for 20 seconds. Notice how it changes your mood!</t>
+          <t>Hug yourself tightly for 5 seconds. Feel cozy and safe!</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -903,22 +903,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -927,41 +927,41 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stand up and stretch like a cat for 10 seconds. Reach high and low!</t>
+          <t>Find 5 blue things around you. Say their names out loud as you point to them!</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -973,78 +973,78 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>March in place while singing 'Row Your Boat' at half speed. Notice how it feels!</t>
+          <t>Take a deep breath in for 4 seconds, hold for 4, then exhale for 4. Repeat 3 times!</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>March in place for 30 seconds, lifting your knees high!</t>
+          <t>Write down one thing you're grateful for today. It can be big or small!</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1053,238 +1053,238 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Name 5 things that are the color blue around you. Take your time looking!</t>
+          <t>Walk like a penguin from one side of the room to the other. Waddle slowly!</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>9</v>
       </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Close your eyes and imagine your favorite place. What do you see, hear, and smell?</t>
+          <t>Stand up and stretch like a cat for 10 seconds. Reach high and low!</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Write a secret note to your future self about today. Hide it under your pillow!</t>
+          <t>Jump in place 10 times to shake out your energy!</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tighten all your muscles for 5 seconds, then relax like a noodle. Repeat!</t>
+          <t>Trace shapes with your finger in the air - try circles, squares, and triangles!</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rub your hands together fast to make warmth, then cup them over your eyes for 10 seconds.</t>
+          <t>Stand up and stretch like a cat waking up from a nap. Reach high and low!</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Write down one thing you're grateful for today. It can be as small as a favorite snack!</t>
+          <t>Pretend you're a tree swaying in the wind - move your arms slowly side to side.</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1293,47 +1293,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hum your favorite song while tapping the rhythm on your knees. Make it a duet!</t>
+          <t>Name 3 things you can touch, 2 you can hear, and 1 you can smell right now.</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hum your favorite song quietly for 30 seconds. Notice how your breathing changes!</t>
+          <t>Make a silly face in the mirror and hold it for 5 seconds. Then try a calm face.</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1343,28 +1343,28 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1373,14 +1373,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Write a short poem about your favorite animal. It can rhyme or not!</t>
+          <t>Fold a piece of paper into a tiny square. How small can you make it?</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1401,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -1413,26 +1413,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Count backwards from 10 like a rocket launch. Blast off when you reach 0!</t>
+          <t>Find 5 blue things around you and name them out loud.</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1441,84 +1441,84 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Trace your hand on paper and write one strength in each finger. You're amazing!</t>
+          <t>Balance a book on your head and walk in a straight line. How far can you go?</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Walk like different animals: stomp like an elephant, tiptoe like a mouse, hop like a frog!</t>
+          <t>Write down one challenge you faced today and how you overcame it.</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1533,11 +1533,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>List 3 things you can see, 2 you can touch, and 1 you can hear right now.</t>
+          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1549,71 +1549,71 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Write down one thing you're proud of today. Fold it into a paper airplane and let it fly!</t>
+          <t>Write a silly sentence using the first letter of each color you see around you!</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>10</v>
       </c>
-      <c r="G29" t="n">
-        <v>5</v>
-      </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Blow on your palm like you're cooling soup. Focus on making your breath steady and slow.</t>
+          <t>Count backwards from 10 slowly while tapping your fingers on the table.</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1626,14 +1626,14 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
         <v>9</v>
       </c>
-      <c r="G30" t="n">
-        <v>4</v>
-      </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
@@ -1653,11 +1653,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Whisper the alphabet backwards starting from Z. How far can you get?</t>
+          <t>Write down one small goal for today and put it where you'll see it.</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Balance on one foot for 15 seconds. Can you stay as still as a statue?</t>
+          <t>Pretend you're a tree in the wind - sway gently from side to side for 30 seconds.</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1706,13 +1706,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
@@ -1724,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1733,75 +1733,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Trace the outline of your hand on paper, then write one strength in each finger.</t>
+          <t>Balance on one foot for 15 seconds. Can you do it with your eyes closed?</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Walk like a penguin for 10 steps—keep your arms by your sides and take tiny waddles!</t>
+          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1813,51 +1813,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stand up and stretch like a cat! Reach high, then low, and wiggle your fingers.</t>
+          <t>List 3 things you can see, 2 things you can touch, and 1 thing you can hear right now.</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Name 3 things you can see, 2 you can touch, and 1 you can hear right now.</t>
+          <t>Press your palms together firmly for 10 seconds like you're squishing playdough. Feel the tension release!</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1869,78 +1869,78 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Close your eyes and name 3 things you can hear, 2 things you can feel, and 1 thing you can smell.</t>
+          <t>Imagine your emotions are weather. Draw what your emotional weather looks like today!</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Squeeze a stress ball or pillow for 10 seconds, then relax. Repeat 3 times.</t>
+          <t>Balance on one foot like a flamingo while counting slowly to 10. Then switch!</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -1949,13 +1949,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -1973,87 +1973,87 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Create a secret handshake with yourself using 3 different moves. Practice until it's perfect!</t>
+          <t>Stand on one foot while naming all the states you know. Switch feet halfway!</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pretend you're a tree in the wind—sway gently side to side for 30 seconds.</t>
+          <t>Stand up and stretch like a cat—reach high, then low. Notice how your body feels!</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
         <v>10</v>
       </c>
-      <c r="G40" t="n">
-        <v>5</v>
-      </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Make a silly face in the mirror and hold it for 5 seconds. Can you make yourself laugh?</t>
+          <t>Hum your favorite song quietly for 30 seconds. How does it make you feel?</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2069,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2093,38 +2093,38 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Trace the alphabet in the air with your finger. Go slowly and focus!</t>
+          <t>Write a secret note to your future self. What would you want to remember?</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>List 3 things you're good at. Say them out loud with confidence!</t>
+          <t>March in place while singing 'Row Your Boat' in your head. Keep the rhythm!</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2146,25 +2146,25 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -2173,29 +2173,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Walk like a penguin across the room, keeping your arms at your sides. Focus on each step!</t>
+          <t>Count backwards from 10 slowly. Imagine each number is a step down a staircase.</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2213,78 +2213,78 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stand on one leg like a flamingo while spelling your name backwards. How long can you balance?</t>
+          <t>Write a short poem about your favorite animal. It doesn't have to rhyme!</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jump like a frog 5 times! Can you land softly each time?</t>
+          <t>Close your eyes and name 4 things you can feel touching your body right now.</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2293,7 +2293,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Do 5 star jumps! Spread your arms and legs wide like a star each time.</t>
+          <t>Write a short poem about your favorite animal.</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2303,28 +2303,28 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2333,14 +2333,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jump in place 10 times like a bouncing ball! Then freeze like a statue.</t>
+          <t>Write a short poem about your favorite animal using just 5 words.</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -2349,53 +2349,53 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stand up and stretch like a cat waking up from a nap. Reach high and low!</t>
+          <t>Trace shapes in the air with your finger. Try a square, circle, and triangle!</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>8</v>
       </c>
-      <c r="G49" t="n">
-        <v>3</v>
-      </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -2413,26 +2413,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Make a silly face in the mirror and hold it for 10 seconds. Notice how it changes your mood!</t>
+          <t>Make a silly face in the mirror and see if you can make yourself laugh!</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2453,38 +2453,38 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Make a silly face in the mirror and hold it for 5 seconds. Then laugh!</t>
+          <t>Take 3 deep breaths and imagine blowing up a balloon with each breath. See how big it can get!</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -2493,26 +2493,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
+          <t>Create a secret handshake with yourself using 4 different moves.</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2533,29 +2533,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Count backwards from 20 slowly. Can you do it while balancing on one foot?</t>
+          <t>Name 3 things you can hear right now. Say them softly to yourself.</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2573,14 +2573,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Balance a book on your head and walk in slow motion across the room. Pretend you're royalty!</t>
+          <t>Make a silly face in the mirror and hold it for 5 seconds. Did you laugh?</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2589,22 +2589,22 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jump in place 10 times like you're popping popcorn. Land softly each time!</t>
+          <t>Press your palms together hard for 5 seconds, then release. Feel the calm!</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2623,56 +2623,56 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Write a secret message to your future self and hide it under your pillow.</t>
+          <t>Write down one thing you're grateful for today and put it in a 'happy jar' to read later.</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Write down one thing you're grateful for today. It can be big or small!</t>
+          <t>Hum your favorite song while tapping the rhythm on your knees.</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2709,19 +2709,19 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
@@ -2733,29 +2733,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Count backwards from 10 slowly. Imagine each number is a step down a staircase.</t>
+          <t>Count backward from 20 while hopping on one foot. Can you do it without stopping?</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
         <v>9</v>
       </c>
-      <c r="G58" t="n">
-        <v>4</v>
-      </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>1</v>
@@ -2773,26 +2773,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jump in place 10 times like a bouncing bunny! Then freeze like a statue for 5 seconds.</t>
+          <t>Do 10 jumping jacks while spelling your full name with each jump.</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H59" t="n">
         <v>2</v>
@@ -2807,93 +2807,93 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fold a piece of paper into fourths. Draw a different emotion in each box: happy, sad, angry, calm.</t>
+          <t>Take a deep breath in for 4 seconds, hold for 4, then breathe out for 4. Repeat 3 times!</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Take 3 deep breaths like you're blowing up a balloon. Feel your belly rise and fall!</t>
+          <t>Walk like a penguin—slow and wobbly—for 10 steps. Then walk normally. Notice the difference!</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
         <v>6</v>
       </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Write down one small goal for today, like 'I'll finish my homework by 4pm.'</t>
+          <t>Whisper the alphabet backward as slowly as you can. Focus on each letter!</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>2</v>
@@ -2933,35 +2933,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Write a secret message to your future self using your non-dominant hand.</t>
+          <t>Hum your favorite song quietly for 30 seconds.</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>7</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2973,78 +2973,78 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Trace your hand on paper and write one strength in each finger. You have 5 superpowers!</t>
+          <t>Close your eyes and listen for 3 sounds around you. What do you hear?</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>7</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hum your favorite song quietly for 30 seconds. Notice how it makes you feel.</t>
+          <t>Count backwards from 20 slowly. Focus on each number!</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3053,51 +3053,51 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Balance a book on your head and walk in a straight line. How far can you go?</t>
+          <t>Walk around the room stepping only on imaginary stepping stones.</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fold a piece of paper into an origami shape. Focus on each fold carefully.</t>
+          <t>Hum your favorite song quietly for 30 seconds. Notice how it makes you feel.</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -3109,22 +3109,22 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -3133,14 +3133,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Write down one thing you're grateful for today and put it in a 'happy jar'.</t>
+          <t>Name 5 things that are the color blue around you right now.</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3149,38 +3149,38 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Write down one small goal for today, like 'help someone' or 'try something new.'</t>
+          <t>Hum your favorite song quietly for 30 seconds. Notice how it changes your mood!</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
@@ -3189,71 +3189,71 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fold a paper airplane and imagine it carrying away any worries when you throw it.</t>
+          <t>Whisper the alphabet backwards from Z. How far can you get?</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Count backward from 10 slowly. Imagine each number floating away like a balloon.</t>
+          <t>Close your eyes and imagine your favorite place. What do you see, hear, and smell?</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3266,22 +3266,22 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>2</v>
@@ -3293,32 +3293,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Draw a picture of how you feel right now. Use colors to show your emotions!</t>
+          <t>Squeeze a soft ball or pillow for 10 seconds, then relax your hands completely.</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -3327,41 +3327,41 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Spin in a circle 3 times slowly, then stop and notice how you feel.</t>
+          <t>List 3 things that make you unique and special. Say them out loud with pride!</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>List 3 things you like about yourself out loud. Say them like you're cheering for a friend!</t>
+          <t>Make a silly face in the mirror and hold it for 10 seconds. Then laugh at yourself!</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3389,22 +3389,22 @@
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>8</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3413,47 +3413,47 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Whisper a kind word to yourself, like 'I can do this!'</t>
+          <t>Tense all your muscles for 5 seconds, then relax completely. Feel the difference!</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
         <v>11</v>
       </c>
-      <c r="G75" t="n">
-        <v>6</v>
-      </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Do 5 jumping jacks like a bouncing bunny! Then freeze like a statue for 10 seconds.</t>
+          <t>Close your eyes and listen for 3 different sounds around you. What do you hear?</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3463,96 +3463,96 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
         <v>6</v>
       </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Close your eyes and count to 10 slowly. Imagine you're floating on a cloud!</t>
+          <t>Take 3 deep breaths and imagine blowing up a balloon with each breath. See how big it can get!</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
         <v>6</v>
       </c>
-      <c r="G77" t="n">
-        <v>1</v>
-      </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Trace the shape of a star with your finger 3 times. Focus on the lines!</t>
+          <t>Count backwards from 10 slowly. Notice how your body feels calmer with each number.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -3573,35 +3573,35 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
+          <t>Stand up and stretch like a cat waking up from a nap. Reach high and low!</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
         <v>7</v>
       </c>
-      <c r="G79" t="n">
-        <v>2</v>
-      </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3613,27 +3613,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Take a deep breath in for 4 seconds, hold for 4, then breathe out for 6. Repeat 3 times!</t>
+          <t>Trace shapes in the air with your finger. Try circles, squares, and triangles!</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
         <v>8</v>
       </c>
-      <c r="G80" t="n">
-        <v>3</v>
-      </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -3641,23 +3641,23 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Close your eyes and listen for 3 different sounds around you. What do you hear?</t>
+          <t>Whisper the alphabet backwards from Z to A. How far can you get?</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -3666,13 +3666,13 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
         <v>11</v>
-      </c>
-      <c r="G81" t="n">
-        <v>6</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3693,14 +3693,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Stand up and stretch like a cat waking up from a nap. Reach high and low!</t>
+          <t>Stand up and stretch like a cat! Arch your back, then stretch your arms high.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -3709,22 +3709,22 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3733,35 +3733,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Press your palms together hard for 5 seconds, then shake them out like wet noodles!</t>
+          <t>Pretend you're a tree swaying in the wind—move your arms slowly side to side.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>7</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3773,38 +3773,38 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pretend you're a tree in the wind. Sway gently side to side for 30 seconds.</t>
+          <t>Trace your hand on paper and write one strength in each finger. You're amazing!</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
       </c>
       <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
         <v>11</v>
       </c>
-      <c r="G84" t="n">
-        <v>6</v>
-      </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -3813,127 +3813,127 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Press your palms together for 10 seconds like you're holding a butterfly. Feel the warmth!</t>
+          <t>Pretend you're a tree in the wind - sway gently from side to side.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Take 3 deep breaths and imagine blowing up a big balloon. Let it go slowly and watch it float away!</t>
+          <t>Name 3 things you can see, 2 you can touch, and 1 you can hear right now.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fold a piece of paper into a simple origami shape. Focus on each fold!</t>
+          <t>Write down one thing you're grateful for today. It can be as small as a sunny day!</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Write down one thing you're grateful for today. It can be big or small!</t>
+          <t>Take a deep breath in for 4 seconds, hold it for 4 seconds, then breathe out for 4 seconds. Repeat 3 times!</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3946,22 +3946,22 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -3973,7 +3973,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
+          <t>Make a silly face in the mirror and laugh at yourself!</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3986,16 +3986,16 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -4007,13 +4007,13 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Rub your palms together fast to make heat, then cup them over your eyes for a warm, dark break.</t>
+          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4023,59 +4023,59 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>8</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Walk backwards slowly for 10 steps. Pay attention to your surroundings!</t>
+          <t>Close your eyes and imagine your favorite place. What do you see, hear, and smell there?</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -4087,17 +4087,17 @@
         <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Whisper the names of all your family members slowly. Send them happy thoughts!</t>
+          <t>Press your palms together hard for 5 seconds, then release. Notice the tension leaving.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -4133,54 +4133,54 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Whisper a silly word 3 times, then laugh like it's the funniest thing ever!</t>
+          <t>Whisper a kind message to yourself like 'I am strong and capable'.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Find 5 blue things around you and touch each one gently. Notice their different textures.</t>
+          <t>Whisper the alphabet backwards while walking heel-to-toe in a straight line.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -4189,13 +4189,13 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -4207,20 +4207,20 @@
         <v>2</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Close your eyes and listen carefully. What's the farthest sound you can hear?</t>
+          <t>Do 5 jumping jacks like a bouncing bunny! Then freeze like a statue for 5 seconds.</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -4229,35 +4229,35 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Hum your favorite song quietly for 20 seconds. Feel the vibrations!</t>
+          <t>Write down one thing you're grateful for today. It can be big or small!</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -4266,16 +4266,16 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4293,14 +4293,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Take a deep breath in for 4 seconds, hold for 4 seconds, then breathe out for 4 seconds. Repeat 3 times!</t>
+          <t>Jump like a frog 5 times! Notice how your energy changes after moving.</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -4309,10 +4309,10 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H97" t="n">
         <v>2</v>
@@ -4324,23 +4324,23 @@
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Take a deep breath in for 4 seconds, hold for 4, then breathe out for 4. Repeat 3 times!</t>
+          <t>Walk slowly around the room stepping only on imaginary lily pads. Don't fall in the 'water'!</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
         <v>2</v>
@@ -4361,10 +4361,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4373,38 +4373,38 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Balance on one foot like a flamingo for 15 seconds. Can you stay still?</t>
+          <t>Write a short poem about your favorite animal using only 5 words.</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4413,14 +4413,14 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
+          <t>Write down one thing you're grateful for today and put it in a 'happy jar'.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4429,13 +4429,13 @@
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4444,23 +4444,23 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Balance on one foot while pretending to be a flamingo. Count slowly to 15!</t>
+          <t>Draw a picture of how you're feeling right now. Use colors to show your emotions!</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4469,13 +4469,13 @@
         <v>1</v>
       </c>
       <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
         <v>6</v>
       </c>
-      <c r="G101" t="n">
-        <v>1</v>
-      </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
